--- a/ex/tabular/fixtures/handmade.xlsx
+++ b/ex/tabular/fixtures/handmade.xlsx
@@ -40,7 +40,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:f>CONCAT("a","b")</x:f>
+        <x:f>"a"&amp;"b"</x:f>
         <x:v>ab</x:v>
       </x:c>
     </x:row>
